--- a/SYK_Model.xlsx
+++ b/SYK_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADC1A14-5F5C-4625-9143-182C124FCDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F989D9C7-6FB3-4063-95FF-51B3A3AA79E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>

--- a/SYK_Model.xlsx
+++ b/SYK_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F989D9C7-6FB3-4063-95FF-51B3A3AA79E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33906CCC-AF88-409D-912B-1078A87EE8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4965" yWindow="0" windowWidth="21600" windowHeight="13185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -7546,14 +7546,14 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="15" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="18" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -17396,7 +17396,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="17">
-        <v>356.24</v>
+        <v>367.54</v>
       </c>
       <c r="D5" s="37" t="s">
         <v>1924</v>
@@ -17419,7 +17419,7 @@
       </c>
       <c r="C7" s="114">
         <f>C5*C6</f>
-        <v>136226.17600000001</v>
+        <v>140547.296</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="C10" s="114">
         <f>C7-C8+C9</f>
-        <v>149478.17600000001</v>
+        <v>153799.296</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>1553</v>
@@ -19838,43 +19838,43 @@
       </c>
       <c r="CQ4" s="103">
         <f>CP4*(1+CQ21)</f>
-        <v>3145.7400000000002</v>
+        <v>3151.4080000000004</v>
       </c>
       <c r="CR4" s="103">
         <f t="shared" ref="CR4:CZ4" si="15">CQ4*(1+CR21)</f>
-        <v>3476.0427000000004</v>
+        <v>3488.6086560000003</v>
       </c>
       <c r="CS4" s="103">
         <f t="shared" si="15"/>
-        <v>3799.3146711000004</v>
+        <v>3847.9353475680005</v>
       </c>
       <c r="CT4" s="103">
         <f t="shared" si="15"/>
-        <v>4122.2564181435</v>
+        <v>4213.4892055869605</v>
       </c>
       <c r="CU4" s="103">
         <f t="shared" si="15"/>
-        <v>4447.9146751768367</v>
+        <v>4582.1695110758192</v>
       </c>
       <c r="CV4" s="103">
         <f t="shared" si="15"/>
-        <v>4781.5082758150993</v>
+        <v>4957.9074109840367</v>
       </c>
       <c r="CW4" s="103">
         <f t="shared" si="15"/>
-        <v>5130.5583799496017</v>
+        <v>5354.5400038627604</v>
       </c>
       <c r="CX4" s="103">
         <f t="shared" si="15"/>
-        <v>5489.6974665460739</v>
+        <v>5772.1941241640561</v>
       </c>
       <c r="CY4" s="103">
         <f t="shared" si="15"/>
-        <v>5731.2441550741014</v>
+        <v>6210.8808776005244</v>
       </c>
       <c r="CZ4" s="103">
         <f t="shared" si="15"/>
-        <v>5903.1814797263241</v>
+        <v>6676.696943420563</v>
       </c>
       <c r="DA4" s="101"/>
       <c r="DB4" s="101"/>
@@ -20041,39 +20041,39 @@
       </c>
       <c r="CR5" s="103">
         <f t="shared" ref="CR5:CZ8" si="16">CQ5*(1+CR22)</f>
-        <v>4224.3885</v>
+        <v>4201.5127500000008</v>
       </c>
       <c r="CS5" s="103">
         <f t="shared" si="16"/>
-        <v>4625.7054074999996</v>
+        <v>4600.6564612500006</v>
       </c>
       <c r="CT5" s="103">
         <f t="shared" si="16"/>
-        <v>5028.1417779524991</v>
+        <v>5000.9135733787507</v>
       </c>
       <c r="CU5" s="103">
         <f t="shared" si="16"/>
-        <v>5445.4775455225563</v>
+        <v>5415.9893999691867</v>
       </c>
       <c r="CV5" s="103">
         <f t="shared" si="16"/>
-        <v>5870.2247940733159</v>
+        <v>5838.436573166784</v>
       </c>
       <c r="CW5" s="103">
         <f t="shared" si="16"/>
-        <v>6304.6214288347419</v>
+        <v>6270.4808795811268</v>
       </c>
       <c r="CX5" s="103">
         <f t="shared" si="16"/>
-        <v>6745.9449288531741</v>
+        <v>6709.4145411518057</v>
       </c>
       <c r="CY5" s="103">
         <f t="shared" si="16"/>
-        <v>7191.1772941574836</v>
+        <v>7152.235900867825</v>
       </c>
       <c r="CZ5" s="103">
         <f t="shared" si="16"/>
-        <v>7622.6479318069332</v>
+        <v>7581.3700549198948</v>
       </c>
       <c r="DA5" s="101"/>
       <c r="DB5" s="101"/>
@@ -20237,43 +20237,43 @@
       </c>
       <c r="CQ6" s="103">
         <f>CP6*(1+CQ23)</f>
-        <v>4133.1959999999999</v>
+        <v>4140.8999999999996</v>
       </c>
       <c r="CR6" s="103">
         <f t="shared" si="16"/>
-        <v>4397.7205439999998</v>
+        <v>4418.3402999999998</v>
       </c>
       <c r="CS6" s="103">
         <f t="shared" si="16"/>
-        <v>4670.3792177280002</v>
+        <v>4696.6957388999999</v>
       </c>
       <c r="CT6" s="103">
         <f t="shared" si="16"/>
-        <v>4950.6019707916803</v>
+        <v>4978.4974832340004</v>
       </c>
       <c r="CU6" s="103">
         <f t="shared" si="16"/>
-        <v>5237.7368850975981</v>
+        <v>5267.2503372615729</v>
       </c>
       <c r="CV6" s="103">
         <f t="shared" si="16"/>
-        <v>5531.0501506630635</v>
+        <v>5562.2163561482212</v>
       </c>
       <c r="CW6" s="103">
         <f t="shared" si="16"/>
-        <v>5829.7268587988692</v>
+        <v>5862.5760393802257</v>
       </c>
       <c r="CX6" s="103">
         <f t="shared" si="16"/>
-        <v>6132.8726554564109</v>
+        <v>6167.4299934279979</v>
       </c>
       <c r="CY6" s="103">
         <f t="shared" si="16"/>
-        <v>6439.5162882292316</v>
+        <v>6475.8014930993977</v>
       </c>
       <c r="CZ6" s="103">
         <f t="shared" si="16"/>
-        <v>6761.4921026406937</v>
+        <v>6799.591567754368</v>
       </c>
       <c r="DA6" s="101"/>
       <c r="DB6" s="101"/>
@@ -20441,39 +20441,39 @@
       </c>
       <c r="CR7" s="103">
         <f t="shared" si="16"/>
-        <v>2435.4638</v>
+        <v>2737.3807999999999</v>
       </c>
       <c r="CS7" s="103">
         <f t="shared" si="16"/>
-        <v>2800.7833699999996</v>
+        <v>3394.3521919999998</v>
       </c>
       <c r="CT7" s="103">
         <f t="shared" si="16"/>
-        <v>3192.8930418</v>
+        <v>4107.16615232</v>
       </c>
       <c r="CU7" s="103">
         <f t="shared" si="16"/>
-        <v>3544.1112763980004</v>
+        <v>4805.3843982143999</v>
       </c>
       <c r="CV7" s="103">
         <f t="shared" si="16"/>
-        <v>3863.0812912738206</v>
+        <v>5526.1920579465595</v>
       </c>
       <c r="CW7" s="103">
         <f t="shared" si="16"/>
-        <v>4172.1277945757265</v>
+        <v>6244.5970254796121</v>
       </c>
       <c r="CX7" s="103">
         <f t="shared" si="16"/>
-        <v>4443.3161012231485</v>
+        <v>6931.5026982823701</v>
       </c>
       <c r="CY7" s="103">
         <f t="shared" si="16"/>
-        <v>4709.9150672965379</v>
+        <v>7624.6529681106076</v>
       </c>
       <c r="CZ7" s="103">
         <f t="shared" si="16"/>
-        <v>4968.9603959978476</v>
+        <v>8310.8717352405638</v>
       </c>
       <c r="DA7" s="101"/>
       <c r="DB7" s="101"/>
@@ -20636,43 +20636,43 @@
       </c>
       <c r="CQ8" s="103">
         <f>CP8*(1+CQ25)</f>
-        <v>2403</v>
+        <v>2947.68</v>
       </c>
       <c r="CR8" s="103">
         <f t="shared" si="16"/>
-        <v>2619.27</v>
+        <v>3566.6927999999998</v>
       </c>
       <c r="CS8" s="103">
         <f t="shared" si="16"/>
-        <v>2828.8116</v>
+        <v>4137.3636479999996</v>
       </c>
       <c r="CT8" s="103">
         <f t="shared" si="16"/>
-        <v>3040.9724699999997</v>
+        <v>4675.2209222399988</v>
       </c>
       <c r="CU8" s="103">
         <f t="shared" si="16"/>
-        <v>3253.8405428999999</v>
+        <v>5189.4952236863992</v>
       </c>
       <c r="CV8" s="103">
         <f t="shared" si="16"/>
-        <v>3471.8478592742999</v>
+        <v>5708.44474605504</v>
       </c>
       <c r="CW8" s="103">
         <f t="shared" si="16"/>
-        <v>3690.5742744085805</v>
+        <v>6165.1203257394436</v>
       </c>
       <c r="CX8" s="103">
         <f t="shared" si="16"/>
-        <v>3919.3898794219126</v>
+        <v>6596.6787485412051</v>
       </c>
       <c r="CY8" s="103">
         <f t="shared" si="16"/>
-        <v>4158.4726620666488</v>
+        <v>6992.4794734536781</v>
       </c>
       <c r="CZ8" s="103">
         <f t="shared" si="16"/>
-        <v>4574.319928273314</v>
+        <v>7342.103447126362</v>
       </c>
       <c r="DA8" s="101"/>
       <c r="DB8" s="101"/>
@@ -20855,43 +20855,43 @@
       </c>
       <c r="CQ9" s="104">
         <f>SUM(CQ4:CQ8)</f>
-        <v>15507.341</v>
+        <v>16065.393000000002</v>
       </c>
       <c r="CR9" s="104">
         <f t="shared" ref="CR9:CZ9" si="19">SUM(CR4:CR8)</f>
-        <v>17152.885544000001</v>
+        <v>18412.535306000002</v>
       </c>
       <c r="CS9" s="104">
         <f t="shared" si="19"/>
-        <v>18724.994266327998</v>
+        <v>20677.003387717999</v>
       </c>
       <c r="CT9" s="104">
         <f t="shared" si="19"/>
-        <v>20334.865678687682</v>
+        <v>22975.287336759713</v>
       </c>
       <c r="CU9" s="104">
         <f t="shared" si="19"/>
-        <v>21929.080925094993</v>
+        <v>25260.288870207376</v>
       </c>
       <c r="CV9" s="104">
         <f t="shared" si="19"/>
-        <v>23517.712371099602</v>
+        <v>27593.197144300641</v>
       </c>
       <c r="CW9" s="104">
         <f t="shared" si="19"/>
-        <v>25127.608736567519</v>
+        <v>29897.314274043169</v>
       </c>
       <c r="CX9" s="104">
         <f t="shared" si="19"/>
-        <v>26731.221031500725</v>
+        <v>32177.220105567434</v>
       </c>
       <c r="CY9" s="104">
         <f t="shared" si="19"/>
-        <v>28230.325466824001</v>
+        <v>34456.050713132034</v>
       </c>
       <c r="CZ9" s="104">
         <f t="shared" si="19"/>
-        <v>29830.601838445113</v>
+        <v>36710.633748461754</v>
       </c>
       <c r="DA9" s="102"/>
       <c r="DB9" s="102"/>
@@ -21051,43 +21051,43 @@
       </c>
       <c r="CQ10" s="103">
         <f>CP10*(1+CQ27)</f>
-        <v>2630.5250000000001</v>
+        <v>2635.4189999999999</v>
       </c>
       <c r="CR10" s="103">
         <f t="shared" ref="CR10:CZ10" si="20">CQ10*(1+CR27)</f>
-        <v>2840.9670000000001</v>
+        <v>2848.8879389999997</v>
       </c>
       <c r="CS10" s="103">
         <f t="shared" si="20"/>
-        <v>3011.4250200000001</v>
+        <v>3019.82121534</v>
       </c>
       <c r="CT10" s="103">
         <f t="shared" si="20"/>
-        <v>3161.9962710000004</v>
+        <v>3170.8122761069999</v>
       </c>
       <c r="CU10" s="103">
         <f t="shared" si="20"/>
-        <v>3288.4761218400004</v>
+        <v>3297.6447671512801</v>
       </c>
       <c r="CV10" s="103">
         <f t="shared" si="20"/>
-        <v>3413.4382144699207</v>
+        <v>3422.9552683030288</v>
       </c>
       <c r="CW10" s="103">
         <f t="shared" si="20"/>
-        <v>3539.7354284053076</v>
+        <v>3549.6046132302404</v>
       </c>
       <c r="CX10" s="103">
         <f t="shared" si="20"/>
-        <v>3667.165903827899</v>
+        <v>3677.3903793065292</v>
       </c>
       <c r="CY10" s="103">
         <f t="shared" si="20"/>
-        <v>3795.5167104618754</v>
+        <v>3806.0990425822574</v>
       </c>
       <c r="CZ10" s="103">
         <f t="shared" si="20"/>
-        <v>3924.5642786175795</v>
+        <v>3935.5064100300542</v>
       </c>
       <c r="DA10" s="101"/>
       <c r="DB10" s="101"/>
@@ -21835,43 +21835,43 @@
       </c>
       <c r="CQ14" s="103">
         <f>CP14*(1+CQ31)</f>
-        <v>774.3</v>
+        <v>932.72</v>
       </c>
       <c r="CR14" s="103">
         <f t="shared" ref="CR14:CZ14" si="24">CQ14*(1+CR31)</f>
-        <v>840.11549999999988</v>
+        <v>1100.6096</v>
       </c>
       <c r="CS14" s="103">
         <f t="shared" si="24"/>
-        <v>898.92358499999989</v>
+        <v>1276.707136</v>
       </c>
       <c r="CT14" s="103">
         <f t="shared" si="24"/>
-        <v>961.84823594999989</v>
+        <v>1455.4461350400002</v>
       </c>
       <c r="CU14" s="103">
         <f t="shared" si="24"/>
-        <v>1029.1776124665</v>
+        <v>1615.5452098944004</v>
       </c>
       <c r="CV14" s="103">
         <f t="shared" si="24"/>
-        <v>1101.2200453391551</v>
+        <v>1744.7888266859525</v>
       </c>
       <c r="CW14" s="103">
         <f t="shared" si="24"/>
-        <v>1178.3054485128962</v>
+        <v>1866.9240445539692</v>
       </c>
       <c r="CX14" s="103">
         <f t="shared" si="24"/>
-        <v>1260.7868299087991</v>
+        <v>1978.9394872272076</v>
       </c>
       <c r="CY14" s="103">
         <f t="shared" si="24"/>
-        <v>1349.0419080024151</v>
+        <v>2077.8864615885682</v>
       </c>
       <c r="CZ14" s="103">
         <f t="shared" si="24"/>
-        <v>1443.4748415625843</v>
+        <v>2161.001920052111</v>
       </c>
       <c r="DA14" s="101"/>
       <c r="DB14" s="101"/>
@@ -22054,43 +22054,43 @@
       </c>
       <c r="CQ15" s="104">
         <f>SUM(CQ10:CQ14)</f>
-        <v>9298.6639999999989</v>
+        <v>9461.9779999999992</v>
       </c>
       <c r="CR15" s="104">
         <f>SUM(CR10:CR14)</f>
-        <v>9909.6455400000013</v>
+        <v>10178.060579000001</v>
       </c>
       <c r="CS15" s="104">
         <f t="shared" ref="CS15:CZ15" si="27">SUM(CS10:CS14)</f>
-        <v>10639.239406920002</v>
+        <v>11025.419153260002</v>
       </c>
       <c r="CT15" s="104">
         <f t="shared" si="27"/>
-        <v>11291.380464621601</v>
+        <v>11793.794368818601</v>
       </c>
       <c r="CU15" s="104">
         <f t="shared" si="27"/>
-        <v>11941.373280476642</v>
+        <v>12536.909523215822</v>
       </c>
       <c r="CV15" s="104">
         <f t="shared" si="27"/>
-        <v>12612.261768004384</v>
+        <v>13265.347603184287</v>
       </c>
       <c r="CW15" s="104">
         <f t="shared" si="27"/>
-        <v>13296.319117846419</v>
+        <v>13994.806898712424</v>
       </c>
       <c r="CX15" s="104">
         <f t="shared" si="27"/>
-        <v>13985.861062406657</v>
+        <v>14714.238195203696</v>
       </c>
       <c r="CY15" s="104">
         <f t="shared" si="27"/>
-        <v>14697.096706011103</v>
+        <v>15436.523591717638</v>
       </c>
       <c r="CZ15" s="104">
         <f t="shared" si="27"/>
-        <v>15430.969271193204</v>
+        <v>16159.438481095205</v>
       </c>
       <c r="DA15" s="102"/>
       <c r="DB15" s="102"/>
@@ -22273,43 +22273,43 @@
       </c>
       <c r="CQ16" s="104">
         <f t="shared" si="30"/>
-        <v>24806.004999999997</v>
+        <v>25527.370999999999</v>
       </c>
       <c r="CR16" s="104">
         <f t="shared" si="30"/>
-        <v>27062.531084000002</v>
+        <v>28590.595885000002</v>
       </c>
       <c r="CS16" s="104">
         <f t="shared" si="30"/>
-        <v>29364.233673248</v>
+        <v>31702.422540978001</v>
       </c>
       <c r="CT16" s="104">
         <f t="shared" si="30"/>
-        <v>31626.246143309283</v>
+        <v>34769.081705578312</v>
       </c>
       <c r="CU16" s="104">
         <f t="shared" si="30"/>
-        <v>33870.454205571637</v>
+        <v>37797.198393423198</v>
       </c>
       <c r="CV16" s="104">
         <f t="shared" si="30"/>
-        <v>36129.974139103986</v>
+        <v>40858.544747484928</v>
       </c>
       <c r="CW16" s="104">
         <f t="shared" si="30"/>
-        <v>38423.927854413938</v>
+        <v>43892.121172755593</v>
       </c>
       <c r="CX16" s="104">
         <f t="shared" si="30"/>
-        <v>40717.082093907382</v>
+        <v>46891.458300771134</v>
       </c>
       <c r="CY16" s="104">
         <f t="shared" si="30"/>
-        <v>42927.422172835104</v>
+        <v>49892.574304849673</v>
       </c>
       <c r="CZ16" s="104">
         <f t="shared" si="30"/>
-        <v>45261.571109638317</v>
+        <v>52870.072229556958</v>
       </c>
       <c r="DA16" s="102"/>
       <c r="DB16" s="102"/>
@@ -22564,43 +22564,43 @@
       </c>
       <c r="CQ18" s="105">
         <f t="shared" ref="CQ18:CZ18" si="34">CQ9/CQ16</f>
-        <v>0.62514463735696268</v>
+        <v>0.62933989559676951</v>
       </c>
       <c r="CR18" s="105">
         <f t="shared" si="34"/>
-        <v>0.6338241419754409</v>
+        <v>0.6440066999673868</v>
       </c>
       <c r="CS18" s="105">
         <f t="shared" si="34"/>
-        <v>0.63768033161332671</v>
+        <v>0.6522215569170231</v>
       </c>
       <c r="CT18" s="105">
         <f t="shared" si="34"/>
-        <v>0.64297436965941157</v>
+        <v>0.66079649532629403</v>
       </c>
       <c r="CU18" s="105">
         <f t="shared" si="34"/>
-        <v>0.64743982445584369</v>
+        <v>0.66831114325665808</v>
       </c>
       <c r="CV18" s="105">
         <f t="shared" si="34"/>
-        <v>0.65091971227419299</v>
+        <v>0.67533479997471413</v>
       </c>
       <c r="CW18" s="105">
         <f t="shared" si="34"/>
-        <v>0.65395731617482189</v>
+        <v>0.68115446406360547</v>
       </c>
       <c r="CX18" s="105">
         <f t="shared" si="34"/>
-        <v>0.65651121487167174</v>
+        <v>0.68620642802738929</v>
       </c>
       <c r="CY18" s="105">
         <f t="shared" si="34"/>
-        <v>0.65762918055415931</v>
+        <v>0.69060478825168226</v>
       </c>
       <c r="CZ18" s="105">
         <f t="shared" si="34"/>
-        <v>0.65907128513470392</v>
+        <v>0.69435565718668935</v>
       </c>
       <c r="DA18" s="102"/>
       <c r="DB18" s="102"/>
@@ -22783,43 +22783,43 @@
       </c>
       <c r="CQ19" s="105">
         <f t="shared" ref="CQ19:CZ19" si="38">CQ15/CQ16</f>
-        <v>0.37485536264303743</v>
+        <v>0.37066010440323055</v>
       </c>
       <c r="CR19" s="105">
         <f t="shared" si="38"/>
-        <v>0.36617585802455904</v>
+        <v>0.35599330003261315</v>
       </c>
       <c r="CS19" s="105">
         <f t="shared" si="38"/>
-        <v>0.36231966838667334</v>
+        <v>0.3477784430829769</v>
       </c>
       <c r="CT19" s="105">
         <f t="shared" si="38"/>
-        <v>0.35702563034058843</v>
+        <v>0.33920350467370608</v>
       </c>
       <c r="CU19" s="105">
         <f t="shared" si="38"/>
-        <v>0.35256017554415625</v>
+        <v>0.33168885674334198</v>
       </c>
       <c r="CV19" s="105">
         <f t="shared" si="38"/>
-        <v>0.34908028772580696</v>
+        <v>0.32466520002528587</v>
       </c>
       <c r="CW19" s="105">
         <f t="shared" si="38"/>
-        <v>0.34604268382517817</v>
+        <v>0.31884553593639448</v>
       </c>
       <c r="CX19" s="105">
         <f t="shared" si="38"/>
-        <v>0.34348878512832831</v>
+        <v>0.3137935719726106</v>
       </c>
       <c r="CY19" s="105">
         <f t="shared" si="38"/>
-        <v>0.34237081944584064</v>
+        <v>0.30939521174831769</v>
       </c>
       <c r="CZ19" s="105">
         <f t="shared" si="38"/>
-        <v>0.34092871486529608</v>
+        <v>0.30564434281331071</v>
       </c>
       <c r="DA19" s="102"/>
       <c r="DB19" s="102"/>
@@ -23058,34 +23058,34 @@
         <v>0.11838989739542227</v>
       </c>
       <c r="CQ21" s="105">
-        <v>0.11</v>
+        <v>0.112</v>
       </c>
       <c r="CR21" s="105">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="CS21" s="105">
-        <v>9.2999999999999999E-2</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="CT21" s="105">
-        <v>8.5000000000000006E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="CU21" s="105">
-        <v>7.9000000000000001E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="CV21" s="105">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="CW21" s="105">
+        <v>0.08</v>
+      </c>
+      <c r="CX21" s="105">
+        <v>7.8E-2</v>
+      </c>
+      <c r="CY21" s="105">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="CZ21" s="105">
         <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="CW21" s="105">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="CX21" s="105">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="CY21" s="105">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="CZ21" s="105">
-        <v>0.03</v>
       </c>
       <c r="DA21" s="101"/>
       <c r="DB21" s="101"/>
@@ -23254,7 +23254,7 @@
         <v>0.125</v>
       </c>
       <c r="CR22" s="105">
-        <v>0.108</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="CS22" s="105">
         <v>9.5000000000000001E-2</v>
@@ -23444,13 +23444,13 @@
         <v>0.11361665221162176</v>
       </c>
       <c r="CQ23" s="105">
-        <v>7.2999999999999995E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="CR23" s="105">
-        <v>6.4000000000000001E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="CS23" s="105">
-        <v>6.2E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="CT23" s="105">
         <v>0.06</v>
@@ -23678,31 +23678,31 @@
         <v>0.54</v>
       </c>
       <c r="CR24" s="105">
+        <v>0.36</v>
+      </c>
+      <c r="CS24" s="105">
+        <v>0.24</v>
+      </c>
+      <c r="CT24" s="105">
         <v>0.21</v>
       </c>
-      <c r="CS24" s="105">
+      <c r="CU24" s="105">
+        <v>0.17</v>
+      </c>
+      <c r="CV24" s="105">
         <v>0.15</v>
       </c>
-      <c r="CT24" s="105">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="CU24" s="105">
+      <c r="CW24" s="105">
+        <v>0.13</v>
+      </c>
+      <c r="CX24" s="105">
         <v>0.11</v>
       </c>
-      <c r="CV24" s="105">
+      <c r="CY24" s="105">
+        <v>0.1</v>
+      </c>
+      <c r="CZ24" s="105">
         <v>0.09</v>
-      </c>
-      <c r="CW24" s="105">
-        <v>0.08</v>
-      </c>
-      <c r="CX24" s="105">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="CY24" s="105">
-        <v>0.06</v>
-      </c>
-      <c r="CZ24" s="105">
-        <v>5.5E-2</v>
       </c>
     </row>
     <row r="25" spans="2:156">
@@ -23854,34 +23854,34 @@
         <v>0.13859275053304909</v>
       </c>
       <c r="CQ25" s="105">
-        <v>0.125</v>
+        <v>0.38</v>
       </c>
       <c r="CR25" s="105">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="CS25" s="105">
+        <v>0.16</v>
+      </c>
+      <c r="CT25" s="105">
+        <v>0.13</v>
+      </c>
+      <c r="CU25" s="105">
+        <v>0.11</v>
+      </c>
+      <c r="CV25" s="105">
+        <v>0.1</v>
+      </c>
+      <c r="CW25" s="105">
         <v>0.08</v>
       </c>
-      <c r="CT25" s="105">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="CU25" s="105">
+      <c r="CX25" s="105">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="CV25" s="105">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="CW25" s="105">
-        <v>6.3E-2</v>
-      </c>
-      <c r="CX25" s="105">
-        <v>6.2E-2</v>
-      </c>
       <c r="CY25" s="105">
-        <v>6.0999999999999999E-2</v>
+        <v>0.06</v>
       </c>
       <c r="CZ25" s="105">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="26" spans="2:156" s="1" customFormat="1" ht="15">
@@ -24040,43 +24040,43 @@
       </c>
       <c r="CQ26" s="106">
         <f>CQ9/CP9-1</f>
-        <v>0.1471623760911378</v>
+        <v>0.18844451841988463</v>
       </c>
       <c r="CR26" s="106">
         <f t="shared" ref="CR26:CZ26" si="45">CR9/CQ9-1</f>
-        <v>0.10611390721336433</v>
+        <v>0.1460992772476839</v>
       </c>
       <c r="CS26" s="106">
         <f t="shared" si="45"/>
-        <v>9.165272620138909E-2</v>
+        <v>0.12298513181832638</v>
       </c>
       <c r="CT26" s="106">
         <f t="shared" si="45"/>
-        <v>8.5974467573248781E-2</v>
+        <v>0.1111516937897723</v>
       </c>
       <c r="CU26" s="106">
         <f t="shared" si="45"/>
-        <v>7.8398120331729437E-2</v>
+        <v>9.945475327273634E-2</v>
       </c>
       <c r="CV26" s="106">
         <f t="shared" si="45"/>
-        <v>7.2444050502209034E-2</v>
+        <v>9.2354774170645193E-2</v>
       </c>
       <c r="CW26" s="106">
         <f t="shared" si="45"/>
-        <v>6.8454632834368923E-2</v>
+        <v>8.3503086564886919E-2</v>
       </c>
       <c r="CX26" s="106">
         <f t="shared" si="45"/>
-        <v>6.3818738652974716E-2</v>
+        <v>7.6257880912857789E-2</v>
       </c>
       <c r="CY26" s="106">
         <f t="shared" si="45"/>
-        <v>5.6080656905148185E-2</v>
+        <v>7.0821239376434031E-2</v>
       </c>
       <c r="CZ26" s="106">
         <f t="shared" si="45"/>
-        <v>5.6686430112247166E-2</v>
+        <v>6.543358825712553E-2</v>
       </c>
       <c r="DA26" s="102"/>
       <c r="DB26" s="102"/>
@@ -24236,10 +24236,10 @@
         <v>7.6550813902331649E-2</v>
       </c>
       <c r="CQ27" s="105">
-        <v>7.4999999999999997E-2</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="CR27" s="105">
-        <v>0.08</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="CS27" s="105">
         <v>0.06</v>
@@ -24776,34 +24776,34 @@
         <v>8.2066869300911893E-2</v>
       </c>
       <c r="CQ31" s="105">
-        <v>8.7499999999999994E-2</v>
+        <v>0.31</v>
       </c>
       <c r="CR31" s="105">
-        <v>8.5000000000000006E-2</v>
+        <v>0.18</v>
       </c>
       <c r="CS31" s="105">
-        <v>7.0000000000000007E-2</v>
+        <v>0.16</v>
       </c>
       <c r="CT31" s="105">
-        <v>7.0000000000000007E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="CU31" s="105">
-        <v>7.0000000000000007E-2</v>
+        <v>0.11</v>
       </c>
       <c r="CV31" s="105">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="CW31" s="105">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="CX31" s="105">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="CY31" s="105">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="CZ31" s="105">
-        <v>7.0000000000000007E-2</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="32" spans="2:156" s="1" customFormat="1" ht="15">
@@ -24918,43 +24918,43 @@
       </c>
       <c r="CQ32" s="106">
         <f>CQ15/CP15-1</f>
-        <v>2.4420403216921738E-2</v>
+        <v>4.2412471080753411E-2</v>
       </c>
       <c r="CR32" s="106">
         <f t="shared" ref="CR32:CZ32" si="50">CR15/CQ15-1</f>
-        <v>6.5706378894860862E-2</v>
+        <v>7.5680008873409088E-2</v>
       </c>
       <c r="CS32" s="106">
         <f t="shared" si="50"/>
-        <v>7.3624617951773885E-2</v>
+        <v>8.3253441820568819E-2</v>
       </c>
       <c r="CT32" s="106">
         <f t="shared" si="50"/>
-        <v>6.1295834482061995E-2</v>
+        <v>6.9691247550566437E-2</v>
       </c>
       <c r="CU32" s="106">
         <f t="shared" si="50"/>
-        <v>5.7565398481754571E-2</v>
+        <v>6.3008997033383141E-2</v>
       </c>
       <c r="CV32" s="106">
         <f t="shared" si="50"/>
-        <v>5.618185377594731E-2</v>
+        <v>5.8103480656021889E-2</v>
       </c>
       <c r="CW32" s="106">
         <f t="shared" si="50"/>
-        <v>5.4237484316841167E-2</v>
+        <v>5.4989836478392284E-2</v>
       </c>
       <c r="CX32" s="106">
         <f t="shared" si="50"/>
-        <v>5.1859611554804674E-2</v>
+        <v>5.1407018453213604E-2</v>
       </c>
       <c r="CY32" s="106">
         <f t="shared" si="50"/>
-        <v>5.0853904556238838E-2</v>
+        <v>4.9087515570420903E-2</v>
       </c>
       <c r="CZ32" s="106">
         <f t="shared" si="50"/>
-        <v>4.99331657035329E-2</v>
+        <v>4.6831456906880398E-2</v>
       </c>
       <c r="DA32" s="102"/>
       <c r="DB32" s="102"/>
@@ -25121,43 +25121,43 @@
       </c>
       <c r="CQ33" s="106">
         <f>CQ16/CP16-1</f>
-        <v>9.7853728701039921E-2</v>
+        <v>0.12977964151360921</v>
       </c>
       <c r="CR33" s="106">
         <f t="shared" ref="CR33:CZ33" si="52">CR16/CQ16-1</f>
-        <v>9.0966928532022928E-2</v>
+        <v>0.11999766388007616</v>
       </c>
       <c r="CS33" s="106">
         <f t="shared" si="52"/>
-        <v>8.5051268194526575E-2</v>
+        <v>0.10884091638015181</v>
       </c>
       <c r="CT33" s="106">
         <f t="shared" si="52"/>
-        <v>7.7032913415413518E-2</v>
+        <v>9.6732644347175656E-2</v>
       </c>
       <c r="CU33" s="106">
         <f t="shared" si="52"/>
-        <v>7.0960304681532138E-2</v>
+        <v>8.7092225025864334E-2</v>
       </c>
       <c r="CV33" s="106">
         <f t="shared" si="52"/>
-        <v>6.6710647569664383E-2</v>
+        <v>8.099400178279903E-2</v>
       </c>
       <c r="CW33" s="106">
         <f t="shared" si="52"/>
-        <v>6.3491706539229753E-2</v>
+        <v>7.4245826522184144E-2</v>
       </c>
       <c r="CX33" s="106">
         <f t="shared" si="52"/>
-        <v>5.9680370215717593E-2</v>
+        <v>6.833429435343108E-2</v>
       </c>
       <c r="CY33" s="106">
         <f t="shared" si="52"/>
-        <v>5.428532609065484E-2</v>
+        <v>6.400133655107898E-2</v>
       </c>
       <c r="CZ33" s="106">
         <f t="shared" si="52"/>
-        <v>5.4374309442701385E-2</v>
+        <v>5.9678177889046502E-2</v>
       </c>
       <c r="DA33" s="102"/>
       <c r="DB33" s="102"/>
@@ -26649,43 +26649,43 @@
       </c>
       <c r="CQ46" s="104">
         <f t="shared" ref="CQ46:CZ46" si="77">CQ16</f>
-        <v>24806.004999999997</v>
+        <v>25527.370999999999</v>
       </c>
       <c r="CR46" s="104">
         <f t="shared" si="77"/>
-        <v>27062.531084000002</v>
+        <v>28590.595885000002</v>
       </c>
       <c r="CS46" s="104">
         <f t="shared" si="77"/>
-        <v>29364.233673248</v>
+        <v>31702.422540978001</v>
       </c>
       <c r="CT46" s="104">
         <f t="shared" si="77"/>
-        <v>31626.246143309283</v>
+        <v>34769.081705578312</v>
       </c>
       <c r="CU46" s="104">
         <f t="shared" si="77"/>
-        <v>33870.454205571637</v>
+        <v>37797.198393423198</v>
       </c>
       <c r="CV46" s="104">
         <f t="shared" si="77"/>
-        <v>36129.974139103986</v>
+        <v>40858.544747484928</v>
       </c>
       <c r="CW46" s="104">
         <f t="shared" si="77"/>
-        <v>38423.927854413938</v>
+        <v>43892.121172755593</v>
       </c>
       <c r="CX46" s="104">
         <f t="shared" si="77"/>
-        <v>40717.082093907382</v>
+        <v>46891.458300771134</v>
       </c>
       <c r="CY46" s="104">
         <f t="shared" si="77"/>
-        <v>42927.422172835104</v>
+        <v>49892.574304849673</v>
       </c>
       <c r="CZ46" s="104">
         <f t="shared" si="77"/>
-        <v>45261.571109638317</v>
+        <v>52870.072229556958</v>
       </c>
       <c r="DA46" s="102"/>
       <c r="DB46" s="102"/>
@@ -27016,43 +27016,43 @@
       </c>
       <c r="CQ47" s="103">
         <f>CQ46*(1-CQ61)</f>
-        <v>9004.5798149999991</v>
+        <v>9266.435673</v>
       </c>
       <c r="CR47" s="103">
         <f t="shared" ref="CR47:CZ47" si="78">CR46*(1-CR61)</f>
-        <v>9661.3235969880006</v>
+        <v>10206.842730945</v>
       </c>
       <c r="CS47" s="103">
         <f t="shared" si="78"/>
-        <v>10394.938720329792</v>
+        <v>11222.657579506213</v>
       </c>
       <c r="CT47" s="103">
         <f t="shared" si="78"/>
-        <v>11069.186150158248</v>
+        <v>12169.178596952408</v>
       </c>
       <c r="CU47" s="103">
         <f t="shared" si="78"/>
-        <v>11753.047609333358</v>
+        <v>13115.627842517848</v>
       </c>
       <c r="CV47" s="103">
         <f t="shared" si="78"/>
-        <v>12428.711103851771</v>
+        <v>14055.339393134815</v>
       </c>
       <c r="CW47" s="103">
         <f t="shared" si="78"/>
-        <v>13064.135470500738</v>
+        <v>14923.3211987369</v>
       </c>
       <c r="CX47" s="103">
         <f t="shared" si="78"/>
-        <v>13721.656665646786</v>
+        <v>15802.421447359871</v>
       </c>
       <c r="CY47" s="103">
         <f t="shared" si="78"/>
-        <v>14337.759005726923</v>
+        <v>16664.119817819788</v>
       </c>
       <c r="CZ47" s="103">
         <f t="shared" si="78"/>
-        <v>14936.318466180643</v>
+        <v>17447.123835753795</v>
       </c>
     </row>
     <row r="48" spans="2:156">
@@ -27393,43 +27393,43 @@
       </c>
       <c r="CQ48" s="103">
         <f>CQ46-CQ47</f>
-        <v>15801.425184999998</v>
+        <v>16260.935326999999</v>
       </c>
       <c r="CR48" s="103">
         <f t="shared" ref="CR48:CZ48" si="103">CR46-CR47</f>
-        <v>17401.207487012001</v>
+        <v>18383.753154055004</v>
       </c>
       <c r="CS48" s="103">
         <f t="shared" si="103"/>
-        <v>18969.294952918208</v>
+        <v>20479.764961471788</v>
       </c>
       <c r="CT48" s="103">
         <f t="shared" si="103"/>
-        <v>20557.059993151037</v>
+        <v>22599.903108625906</v>
       </c>
       <c r="CU48" s="103">
         <f t="shared" si="103"/>
-        <v>22117.406596238281</v>
+        <v>24681.570550905351</v>
       </c>
       <c r="CV48" s="103">
         <f t="shared" si="103"/>
-        <v>23701.263035252217</v>
+        <v>26803.205354350113</v>
       </c>
       <c r="CW48" s="103">
         <f t="shared" si="103"/>
-        <v>25359.792383913198</v>
+        <v>28968.799974018693</v>
       </c>
       <c r="CX48" s="103">
         <f t="shared" si="103"/>
-        <v>26995.425428260598</v>
+        <v>31089.036853411264</v>
       </c>
       <c r="CY48" s="103">
         <f t="shared" si="103"/>
-        <v>28589.663167108181</v>
+        <v>33228.454487029885</v>
       </c>
       <c r="CZ48" s="103">
         <f t="shared" si="103"/>
-        <v>30325.252643457672</v>
+        <v>35422.948393803163</v>
       </c>
     </row>
     <row r="49" spans="2:156">
@@ -27708,43 +27708,43 @@
       </c>
       <c r="CQ49" s="103">
         <f>CQ46*CQ62</f>
-        <v>1686.80834</v>
+        <v>1735.861228</v>
       </c>
       <c r="CR49" s="103">
         <f t="shared" ref="CR49:CZ49" si="115">CR46*CR62</f>
-        <v>1840.2521137120002</v>
+        <v>1944.1605201800003</v>
       </c>
       <c r="CS49" s="103">
         <f t="shared" si="115"/>
-        <v>1996.7678897808642</v>
+        <v>2155.7647327865043</v>
       </c>
       <c r="CT49" s="103">
         <f t="shared" si="115"/>
-        <v>2150.5847377450314</v>
+        <v>2364.2975559793254</v>
       </c>
       <c r="CU49" s="103">
         <f t="shared" si="115"/>
-        <v>2303.1908859788714</v>
+        <v>2570.2094907527776</v>
       </c>
       <c r="CV49" s="103">
         <f t="shared" si="115"/>
-        <v>2456.838241459071</v>
+        <v>2778.3810428289753</v>
       </c>
       <c r="CW49" s="103">
         <f t="shared" si="115"/>
-        <v>2612.8270941001479</v>
+        <v>2984.6642397473806</v>
       </c>
       <c r="CX49" s="103">
         <f t="shared" si="115"/>
-        <v>2768.7615823857022</v>
+        <v>3188.6191644524374</v>
       </c>
       <c r="CY49" s="103">
         <f t="shared" si="115"/>
-        <v>2919.0647077527874</v>
+        <v>3392.6950527297781</v>
       </c>
       <c r="CZ49" s="103">
         <f t="shared" si="115"/>
-        <v>3077.7868354554057</v>
+        <v>3595.1649116098733</v>
       </c>
     </row>
     <row r="50" spans="2:156">
@@ -28023,43 +28023,43 @@
       </c>
       <c r="CQ50" s="103">
         <f>CQ46*CQ63</f>
-        <v>8558.071724999998</v>
+        <v>8806.9429949999994</v>
       </c>
       <c r="CR50" s="103">
         <f t="shared" ref="CR50:CZ50" si="116">CR46*CR63</f>
-        <v>9309.5106928959995</v>
+        <v>9835.1649844399999</v>
       </c>
       <c r="CS50" s="103">
         <f t="shared" si="116"/>
-        <v>10042.567916250817</v>
+        <v>10842.228509014478</v>
       </c>
       <c r="CT50" s="103">
         <f t="shared" si="116"/>
-        <v>10752.923688725157</v>
+        <v>11821.487779896626</v>
       </c>
       <c r="CU50" s="103">
         <f t="shared" si="116"/>
-        <v>11177.249887838641</v>
+        <v>12473.075469829655</v>
       </c>
       <c r="CV50" s="103">
         <f t="shared" si="116"/>
-        <v>11814.501543487004</v>
+        <v>13360.744132427571</v>
       </c>
       <c r="CW50" s="103">
         <f t="shared" si="116"/>
-        <v>12487.776552684531</v>
+        <v>14264.939381145568</v>
       </c>
       <c r="CX50" s="103">
         <f t="shared" si="116"/>
-        <v>13192.334598425992</v>
+        <v>15192.832489449847</v>
       </c>
       <c r="CY50" s="103">
         <f t="shared" si="116"/>
-        <v>13865.557361825739</v>
+        <v>16115.301500466445</v>
       </c>
       <c r="CZ50" s="103">
         <f t="shared" si="116"/>
-        <v>14710.010610632453</v>
+        <v>17182.773474606012</v>
       </c>
     </row>
     <row r="51" spans="2:156">
@@ -29030,43 +29030,43 @@
       </c>
       <c r="CQ53" s="103">
         <f>CQ48-SUM(CQ49:CQ52)</f>
-        <v>4449.8551200000002</v>
+        <v>4611.4411039999995</v>
       </c>
       <c r="CR53" s="103">
         <f t="shared" ref="CR53:CZ53" si="142">CR48-SUM(CR49:CR52)</f>
-        <v>5111.5539804040018</v>
+        <v>5464.5369494350052</v>
       </c>
       <c r="CS53" s="103">
         <f t="shared" si="142"/>
-        <v>5755.8717258865272</v>
+        <v>6307.684298670807</v>
       </c>
       <c r="CT53" s="103">
         <f t="shared" si="142"/>
-        <v>6444.2415230508468</v>
+        <v>7204.8077291199534</v>
       </c>
       <c r="CU53" s="103">
         <f t="shared" si="142"/>
-        <v>7391.3764774818683</v>
+        <v>8392.6962453840188</v>
       </c>
       <c r="CV53" s="103">
         <f t="shared" si="142"/>
-        <v>8146.9662250190759</v>
+        <v>9381.1231538064967</v>
       </c>
       <c r="CW53" s="103">
         <f t="shared" si="142"/>
-        <v>8937.7430010828393</v>
+        <v>10397.750617080063</v>
       </c>
       <c r="CX53" s="103">
         <f t="shared" si="142"/>
-        <v>9673.2401393218533</v>
+        <v>11346.49609138193</v>
       </c>
       <c r="CY53" s="103">
         <f t="shared" si="142"/>
-        <v>10403.119316158794</v>
+        <v>12318.536152462802</v>
       </c>
       <c r="CZ53" s="103">
         <f t="shared" si="142"/>
-        <v>11093.475762557828</v>
+        <v>13201.030572775289</v>
       </c>
     </row>
     <row r="54" spans="2:156">
@@ -29722,43 +29722,43 @@
       </c>
       <c r="CQ55" s="103">
         <f>CQ53+CQ54</f>
-        <v>4869.8351199999997</v>
+        <v>5031.4211039999991</v>
       </c>
       <c r="CR55" s="103">
         <f t="shared" ref="CR55:CZ55" si="167">CR53+CR54</f>
-        <v>5573.5319804040018</v>
+        <v>5926.5149494350053</v>
       </c>
       <c r="CS55" s="103">
         <f t="shared" si="167"/>
-        <v>6264.0475258865272</v>
+        <v>6815.860098670807</v>
       </c>
       <c r="CT55" s="103">
         <f t="shared" si="167"/>
-        <v>7003.2349030508467</v>
+        <v>7763.8011091199533</v>
       </c>
       <c r="CU55" s="103">
         <f t="shared" si="167"/>
-        <v>8006.2691954818683</v>
+        <v>9007.5889633840197</v>
       </c>
       <c r="CV55" s="103">
         <f t="shared" si="167"/>
-        <v>8823.348214819076</v>
+        <v>10057.505143606497</v>
       </c>
       <c r="CW55" s="103">
         <f t="shared" si="167"/>
-        <v>9681.7631898628388</v>
+        <v>11141.770805860062</v>
       </c>
       <c r="CX55" s="103">
         <f t="shared" si="167"/>
-        <v>10491.662346979854</v>
+        <v>12164.918299039931</v>
       </c>
       <c r="CY55" s="103">
         <f t="shared" si="167"/>
-        <v>11303.383744582596</v>
+        <v>13218.800580886604</v>
       </c>
       <c r="CZ55" s="103">
         <f t="shared" si="167"/>
-        <v>12083.766633824009</v>
+        <v>14191.32144404147</v>
       </c>
     </row>
     <row r="56" spans="2:156">
@@ -30037,43 +30037,43 @@
       </c>
       <c r="CQ56" s="103">
         <f>CQ55*CQ65</f>
-        <v>740.21493823999992</v>
+        <v>764.7760078079998</v>
       </c>
       <c r="CR56" s="103">
         <f t="shared" ref="CR56:CZ56" si="168">CR55*CR65</f>
-        <v>808.16213715858021</v>
+        <v>859.34466766807566</v>
       </c>
       <c r="CS56" s="103">
         <f t="shared" si="168"/>
-        <v>876.96665362411386</v>
+        <v>954.22041381391307</v>
       </c>
       <c r="CT56" s="103">
         <f t="shared" si="168"/>
-        <v>980.45288642711864</v>
+        <v>1086.9321552767935</v>
       </c>
       <c r="CU56" s="103">
         <f t="shared" si="168"/>
-        <v>1120.8776873674617</v>
+        <v>1261.0624548737628</v>
       </c>
       <c r="CV56" s="103">
         <f t="shared" si="168"/>
-        <v>1235.2687500746708</v>
+        <v>1408.0507201049097</v>
       </c>
       <c r="CW56" s="103">
         <f t="shared" si="168"/>
-        <v>1355.4468465807975</v>
+        <v>1559.8479128204087</v>
       </c>
       <c r="CX56" s="103">
         <f t="shared" si="168"/>
-        <v>1468.8327285771798</v>
+        <v>1703.0885618655905</v>
       </c>
       <c r="CY56" s="103">
         <f t="shared" si="168"/>
-        <v>1582.4737242415636</v>
+        <v>1850.6320813241248</v>
       </c>
       <c r="CZ56" s="103">
         <f t="shared" si="168"/>
-        <v>1691.7273287353614</v>
+        <v>1986.785002165806</v>
       </c>
     </row>
     <row r="57" spans="2:156" s="1" customFormat="1" ht="15">
@@ -30432,243 +30432,243 @@
       </c>
       <c r="CQ57" s="104">
         <f>CQ55-CQ56</f>
-        <v>4129.6201817599995</v>
+        <v>4266.6450961919991</v>
       </c>
       <c r="CR57" s="104">
         <f>CR55-CR56</f>
-        <v>4765.3698432454221</v>
+        <v>5067.1702817669293</v>
       </c>
       <c r="CS57" s="104">
         <f>CS55-CS56</f>
-        <v>5387.0808722624133</v>
+        <v>5861.6396848568938</v>
       </c>
       <c r="CT57" s="104">
         <f t="shared" ref="CT57:CZ57" si="192">CT55-CT56</f>
-        <v>6022.7820166237279</v>
+        <v>6676.8689538431599</v>
       </c>
       <c r="CU57" s="104">
         <f t="shared" si="192"/>
-        <v>6885.3915081144069</v>
+        <v>7746.5265085102565</v>
       </c>
       <c r="CV57" s="104">
         <f t="shared" si="192"/>
-        <v>7588.0794647444054</v>
+        <v>8649.4544235015874</v>
       </c>
       <c r="CW57" s="104">
         <f t="shared" si="192"/>
-        <v>8326.316343282042</v>
+        <v>9581.922893039653</v>
       </c>
       <c r="CX57" s="104">
         <f t="shared" si="192"/>
-        <v>9022.8296184026749</v>
+        <v>10461.829737174341</v>
       </c>
       <c r="CY57" s="104">
         <f t="shared" si="192"/>
-        <v>9720.9100203410326</v>
+        <v>11368.168499562478</v>
       </c>
       <c r="CZ57" s="104">
         <f t="shared" si="192"/>
-        <v>10392.039305088647</v>
+        <v>12204.536441875665</v>
       </c>
       <c r="DA57" s="104">
         <f t="shared" ref="DA57:EF57" si="193">CZ57*(1+$CZ$71)</f>
-        <v>10636.252228758231</v>
+        <v>12491.343048259745</v>
       </c>
       <c r="DB57" s="104">
         <f t="shared" si="193"/>
-        <v>10886.20415613405</v>
+        <v>12784.889609893849</v>
       </c>
       <c r="DC57" s="104">
         <f t="shared" si="193"/>
-        <v>11142.029953803201</v>
+        <v>13085.334515726356</v>
       </c>
       <c r="DD57" s="104">
         <f t="shared" si="193"/>
-        <v>11403.867657717577</v>
+        <v>13392.839876845926</v>
       </c>
       <c r="DE57" s="104">
         <f t="shared" si="193"/>
-        <v>11671.858547673941</v>
+        <v>13707.571613951806</v>
       </c>
       <c r="DF57" s="104">
         <f t="shared" si="193"/>
-        <v>11946.14722354428</v>
+        <v>14029.699546879674</v>
       </c>
       <c r="DG57" s="104">
         <f t="shared" si="193"/>
-        <v>12226.881683297572</v>
+        <v>14359.397486231348</v>
       </c>
       <c r="DH57" s="104">
         <f t="shared" si="193"/>
-        <v>12514.213402855066</v>
+        <v>14696.843327157785</v>
       </c>
       <c r="DI57" s="104">
         <f t="shared" si="193"/>
-        <v>12808.297417822161</v>
+        <v>15042.219145345995</v>
       </c>
       <c r="DJ57" s="104">
         <f t="shared" si="193"/>
-        <v>13109.292407140983</v>
+        <v>15395.711295261626</v>
       </c>
       <c r="DK57" s="104">
         <f t="shared" si="193"/>
-        <v>13417.360778708797</v>
+        <v>15757.510510700276</v>
       </c>
       <c r="DL57" s="104">
         <f t="shared" si="193"/>
-        <v>13732.668757008454</v>
+        <v>16127.812007701734</v>
       </c>
       <c r="DM57" s="104">
         <f t="shared" si="193"/>
-        <v>14055.386472798155</v>
+        <v>16506.815589882724</v>
       </c>
       <c r="DN57" s="104">
         <f t="shared" si="193"/>
-        <v>14385.688054908913</v>
+        <v>16894.72575624497</v>
       </c>
       <c r="DO57" s="104">
         <f t="shared" si="193"/>
-        <v>14723.751724199274</v>
+        <v>17291.75181151673</v>
       </c>
       <c r="DP57" s="104">
         <f t="shared" si="193"/>
-        <v>15069.759889717958</v>
+        <v>17698.107979087374</v>
       </c>
       <c r="DQ57" s="104">
         <f t="shared" si="193"/>
-        <v>15423.899247126332</v>
+        <v>18114.013516595929</v>
       </c>
       <c r="DR57" s="104">
         <f t="shared" si="193"/>
-        <v>15786.360879433802</v>
+        <v>18539.692834235935</v>
       </c>
       <c r="DS57" s="104">
         <f t="shared" si="193"/>
-        <v>16157.340360100497</v>
+        <v>18975.375615840479</v>
       </c>
       <c r="DT57" s="104">
         <f t="shared" si="193"/>
-        <v>16537.03785856286</v>
+        <v>19421.296942812733</v>
       </c>
       <c r="DU57" s="104">
         <f t="shared" si="193"/>
-        <v>16925.658248239088</v>
+        <v>19877.697420968834</v>
       </c>
       <c r="DV57" s="104">
         <f t="shared" si="193"/>
-        <v>17323.411217072706</v>
+        <v>20344.823310361604</v>
       </c>
       <c r="DW57" s="104">
         <f t="shared" si="193"/>
-        <v>17730.511380673917</v>
+        <v>20822.926658155102</v>
       </c>
       <c r="DX57" s="104">
         <f t="shared" si="193"/>
-        <v>18147.178398119755</v>
+        <v>21312.26543462175</v>
       </c>
       <c r="DY57" s="104">
         <f t="shared" si="193"/>
-        <v>18573.637090475571</v>
+        <v>21813.103672335361</v>
       </c>
       <c r="DZ57" s="104">
         <f t="shared" si="193"/>
-        <v>19010.11756210175</v>
+        <v>22325.711608635243</v>
       </c>
       <c r="EA57" s="104">
         <f t="shared" si="193"/>
-        <v>19456.855324811142</v>
+        <v>22850.365831438172</v>
       </c>
       <c r="EB57" s="104">
         <f t="shared" si="193"/>
-        <v>19914.091424944207</v>
+        <v>23387.349428476969</v>
       </c>
       <c r="EC57" s="104">
         <f t="shared" si="193"/>
-        <v>20382.072573430396</v>
+        <v>23936.952140046182</v>
       </c>
       <c r="ED57" s="104">
         <f t="shared" si="193"/>
-        <v>20861.051278906012</v>
+        <v>24499.470515337271</v>
       </c>
       <c r="EE57" s="104">
         <f t="shared" si="193"/>
-        <v>21351.285983960304</v>
+        <v>25075.208072447698</v>
       </c>
       <c r="EF57" s="104">
         <f t="shared" si="193"/>
-        <v>21853.041204583373</v>
+        <v>25664.475462150222</v>
       </c>
       <c r="EG57" s="104">
         <f t="shared" ref="EG57:EX57" si="194">EF57*(1+$CZ$71)</f>
-        <v>22366.587672891084</v>
+        <v>26267.590635510755</v>
       </c>
       <c r="EH57" s="104">
         <f t="shared" si="194"/>
-        <v>22892.202483204026</v>
+        <v>26884.879015445258</v>
       </c>
       <c r="EI57" s="104">
         <f t="shared" si="194"/>
-        <v>23430.169241559321</v>
+        <v>27516.673672308225</v>
       </c>
       <c r="EJ57" s="104">
         <f t="shared" si="194"/>
-        <v>23980.778218735966</v>
+        <v>28163.315503607471</v>
       </c>
       <c r="EK57" s="104">
         <f t="shared" si="194"/>
-        <v>24544.326506876263</v>
+        <v>28825.153417942249</v>
       </c>
       <c r="EL57" s="104">
         <f t="shared" si="194"/>
-        <v>25121.118179787856</v>
+        <v>29502.544523263892</v>
       </c>
       <c r="EM57" s="104">
         <f t="shared" si="194"/>
-        <v>25711.464457012873</v>
+        <v>30195.854319560596</v>
       </c>
       <c r="EN57" s="104">
         <f t="shared" si="194"/>
-        <v>26315.683871752677</v>
+        <v>30905.456896070271</v>
       </c>
       <c r="EO57" s="104">
         <f t="shared" si="194"/>
-        <v>26934.102442738866</v>
+        <v>31631.735133127924</v>
       </c>
       <c r="EP57" s="104">
         <f t="shared" si="194"/>
-        <v>27567.053850143231</v>
+        <v>32375.080908756434</v>
       </c>
       <c r="EQ57" s="104">
         <f t="shared" si="194"/>
-        <v>28214.879615621598</v>
+        <v>33135.89531011221</v>
       </c>
       <c r="ER57" s="104">
         <f t="shared" si="194"/>
-        <v>28877.929286588707</v>
+        <v>33914.588849899847</v>
       </c>
       <c r="ES57" s="104">
         <f t="shared" si="194"/>
-        <v>29556.560624823545</v>
+        <v>34711.581687872495</v>
       </c>
       <c r="ET57" s="104">
         <f t="shared" si="194"/>
-        <v>30251.139799506902</v>
+        <v>35527.303857537503</v>
       </c>
       <c r="EU57" s="104">
         <f t="shared" si="194"/>
-        <v>30962.041584795315</v>
+        <v>36362.195498189634</v>
       </c>
       <c r="EV57" s="104">
         <f t="shared" si="194"/>
-        <v>31689.649562038008</v>
+        <v>37216.707092397097</v>
       </c>
       <c r="EW57" s="104">
         <f t="shared" si="194"/>
-        <v>32434.356326745903</v>
+        <v>38091.299709068429</v>
       </c>
       <c r="EX57" s="104">
         <f t="shared" si="194"/>
-        <v>33196.563700424435</v>
+        <v>38986.445252231541</v>
       </c>
       <c r="EY57" s="102"/>
       <c r="EZ57" s="102"/>
@@ -32796,43 +32796,43 @@
       </c>
       <c r="CQ64" s="105">
         <f>CQ53/CQ46</f>
-        <v>0.17938620588039067</v>
+        <v>0.18064692615624225</v>
       </c>
       <c r="CR64" s="105">
         <f t="shared" ref="CR64:CZ64" si="216">CR53/CR46</f>
-        <v>0.18887937586244738</v>
+        <v>0.19113057214389725</v>
       </c>
       <c r="CS64" s="105">
         <f t="shared" si="216"/>
-        <v>0.19601641200432068</v>
+        <v>0.19896537214206908</v>
       </c>
       <c r="CT64" s="105">
         <f t="shared" si="216"/>
-        <v>0.20376245393935769</v>
+        <v>0.20721880980722082</v>
       </c>
       <c r="CU64" s="105">
         <f t="shared" si="216"/>
-        <v>0.21822489986762558</v>
+        <v>0.22204545844975557</v>
       </c>
       <c r="CV64" s="105">
         <f t="shared" si="216"/>
-        <v>0.22549050806547624</v>
+        <v>0.22960003132230883</v>
       </c>
       <c r="CW64" s="105">
         <f t="shared" si="216"/>
-        <v>0.23260878052205999</v>
+        <v>0.23689332707698074</v>
       </c>
       <c r="CX64" s="105">
         <f t="shared" si="216"/>
-        <v>0.23757203713694625</v>
+        <v>0.2419736238229839</v>
       </c>
       <c r="CY64" s="105">
         <f t="shared" si="216"/>
-        <v>0.24234204593682757</v>
+        <v>0.24690119369658206</v>
       </c>
       <c r="CZ64" s="105">
         <f t="shared" si="216"/>
-        <v>0.24509701034649911</v>
+        <v>0.24968815089674243</v>
       </c>
     </row>
     <row r="65" spans="2:156">
@@ -33540,43 +33540,43 @@
       </c>
       <c r="CQ66" s="105">
         <f>CQ57/CQ46</f>
-        <v>0.16647663264439397</v>
+        <v>0.1671400120361787</v>
       </c>
       <c r="CR66" s="105">
         <f t="shared" ref="CR66:CZ66" si="225">CR57/CR46</f>
-        <v>0.17608736701138866</v>
+        <v>0.17723206267363634</v>
       </c>
       <c r="CS66" s="105">
         <f t="shared" si="225"/>
-        <v>0.18345722664542957</v>
+        <v>0.18489563935627443</v>
       </c>
       <c r="CT66" s="105">
         <f t="shared" si="225"/>
-        <v>0.19043619623184027</v>
+        <v>0.19203466488940749</v>
       </c>
       <c r="CU66" s="105">
         <f t="shared" si="225"/>
-        <v>0.20328606951428985</v>
+        <v>0.20494975389123471</v>
       </c>
       <c r="CV66" s="105">
         <f t="shared" si="225"/>
-        <v>0.21002172422071344</v>
+        <v>0.2116926698431669</v>
       </c>
       <c r="CW66" s="105">
         <f t="shared" si="225"/>
-        <v>0.21669612682050565</v>
+        <v>0.21830621617319504</v>
       </c>
       <c r="CX66" s="105">
         <f t="shared" si="225"/>
-        <v>0.2215981390216758</v>
+        <v>0.2231073657396212</v>
       </c>
       <c r="CY66" s="105">
         <f t="shared" si="225"/>
-        <v>0.22644988979777408</v>
+        <v>0.22785291514728406</v>
       </c>
       <c r="CZ66" s="105">
         <f t="shared" si="225"/>
-        <v>0.22959961508882959</v>
+        <v>0.23084016963102866</v>
       </c>
     </row>
     <row r="68" spans="2:156">
@@ -33724,43 +33724,43 @@
       </c>
       <c r="CQ68" s="103">
         <f t="shared" ref="CQ68:CZ68" si="232">CP68+CQ57</f>
-        <v>7781.6201817599995</v>
+        <v>7918.6450961919991</v>
       </c>
       <c r="CR68" s="103">
         <f t="shared" si="232"/>
-        <v>12546.990025005422</v>
+        <v>12985.815377958928</v>
       </c>
       <c r="CS68" s="103">
         <f t="shared" si="232"/>
-        <v>17934.070897267833</v>
+        <v>18847.455062815821</v>
       </c>
       <c r="CT68" s="103">
         <f t="shared" si="232"/>
-        <v>23956.852913891562</v>
+        <v>25524.324016658982</v>
       </c>
       <c r="CU68" s="103">
         <f t="shared" si="232"/>
-        <v>30842.24442200597</v>
+        <v>33270.85052516924</v>
       </c>
       <c r="CV68" s="103">
         <f t="shared" si="232"/>
-        <v>38430.323886750375</v>
+        <v>41920.304948670826</v>
       </c>
       <c r="CW68" s="103">
         <f t="shared" si="232"/>
-        <v>46756.640230032419</v>
+        <v>51502.227841710483</v>
       </c>
       <c r="CX68" s="103">
         <f t="shared" si="232"/>
-        <v>55779.469848435096</v>
+        <v>61964.057578884822</v>
       </c>
       <c r="CY68" s="103">
         <f t="shared" si="232"/>
-        <v>65500.37986877613</v>
+        <v>73332.226078447304</v>
       </c>
       <c r="CZ68" s="103">
         <f t="shared" si="232"/>
-        <v>75892.419173864779</v>
+        <v>85536.762520322969</v>
       </c>
     </row>
     <row r="69" spans="2:156">
@@ -34250,7 +34250,7 @@
       </c>
       <c r="CR72" s="103">
         <f>(CQ53)*(1-CQ65)</f>
-        <v>3773.47714176</v>
+        <v>3910.5020561919996</v>
       </c>
       <c r="CT72" s="112">
         <f>SUM(CO68:CO73)-SUM(CO81)+CO74+CO76+CO75</f>
@@ -34373,7 +34373,7 @@
       </c>
       <c r="CR73" s="105">
         <f>CR72/CW72</f>
-        <v>0.10641803609126033</v>
+        <v>0.11028235585301333</v>
       </c>
       <c r="CY73" s="110" t="s">
         <v>1536</v>
@@ -34813,7 +34813,7 @@
       </c>
       <c r="CZ77" s="103">
         <f>NPV(CZ75,CQ57:EX57)</f>
-        <v>135426.60417017774</v>
+        <v>156757.67649193527</v>
       </c>
     </row>
     <row r="78" spans="2:156" ht="15" customHeight="1">
@@ -35069,7 +35069,7 @@
       </c>
       <c r="CZ79" s="107">
         <f>CZ77/CZ78</f>
-        <v>354.14906948268242</v>
+        <v>409.93116237430775</v>
       </c>
       <c r="DA79" s="101"/>
       <c r="DB79" s="102"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="CZ80" s="107">
         <f>Main!C5</f>
-        <v>356.24</v>
+        <v>367.54</v>
       </c>
     </row>
     <row r="81" spans="2:156" ht="15" customHeight="1">
@@ -35241,11 +35241,11 @@
       </c>
       <c r="CZ81" s="111">
         <f>CZ79/CZ80-1</f>
-        <v>-5.8694434014080477E-3</v>
+        <v>0.11533754795208062</v>
       </c>
       <c r="DA81" s="113" t="str">
         <f>IF(CZ81&gt;0,"Upside","Downside")</f>
-        <v>Downside</v>
+        <v>Upside</v>
       </c>
     </row>
     <row r="82" spans="2:156" ht="15" customHeight="1">
@@ -35353,7 +35353,7 @@
       <c r="CW82" s="102"/>
       <c r="CY82" s="115" t="str" cm="1">
         <f t="array" ref="CY82">_xlfn.IFS(CZ81&gt;=25%,"Strong Buy",CZ81&gt;=10.00001%,"Buy",AND(CZ81&lt;=10%,CZ81&gt;=-4.9999%),"Hold",AND(CZ81&lt;=-5%,CZ81&gt;=-14.999999%),"Sell",CZ81&lt;=-15%,"Strong Sell")</f>
-        <v>Hold</v>
+        <v>Buy</v>
       </c>
       <c r="CZ82" s="115"/>
     </row>
@@ -67718,10 +67718,10 @@
       <c r="B2" s="80" t="s">
         <v>1625</v>
       </c>
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="118" t="s">
         <v>1624</v>
       </c>
-      <c r="D2" s="116"/>
+      <c r="D2" s="118"/>
       <c r="E2" s="81" t="s">
         <v>1621</v>
       </c>
@@ -67748,10 +67748,10 @@
       <c r="B4" s="70">
         <v>3.3750000000000002E-2</v>
       </c>
-      <c r="C4" s="118">
+      <c r="C4" s="116">
         <v>45962</v>
       </c>
-      <c r="D4" s="118"/>
+      <c r="D4" s="116"/>
       <c r="E4" s="75">
         <v>750</v>
       </c>
@@ -67778,10 +67778,10 @@
       <c r="B6" s="70">
         <v>4.5499999999999999E-2</v>
       </c>
-      <c r="C6" s="118">
+      <c r="C6" s="116">
         <v>46428</v>
       </c>
-      <c r="D6" s="118"/>
+      <c r="D6" s="116"/>
       <c r="E6" s="75">
         <v>497</v>
       </c>
@@ -67808,10 +67808,10 @@
       <c r="B8" s="70">
         <v>4.7E-2</v>
       </c>
-      <c r="C8" s="118">
+      <c r="C8" s="116">
         <v>46793</v>
       </c>
-      <c r="D8" s="118"/>
+      <c r="D8" s="116"/>
       <c r="E8" s="75">
         <v>696</v>
       </c>
@@ -67838,10 +67838,10 @@
       <c r="B10" s="70">
         <v>4.8500000000000001E-2</v>
       </c>
-      <c r="C10" s="118">
+      <c r="C10" s="116">
         <v>47095</v>
       </c>
-      <c r="D10" s="118"/>
+      <c r="D10" s="116"/>
       <c r="E10" s="75">
         <v>596</v>
       </c>
@@ -67868,10 +67868,10 @@
       <c r="B12" s="70">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="C12" s="118">
+      <c r="C12" s="116">
         <v>47178</v>
       </c>
-      <c r="D12" s="118"/>
+      <c r="D12" s="116"/>
       <c r="E12" s="75">
         <v>863</v>
       </c>
@@ -67898,10 +67898,10 @@
       <c r="B14" s="70">
         <v>4.8500000000000001E-2</v>
       </c>
-      <c r="C14" s="118">
+      <c r="C14" s="116">
         <v>47524</v>
       </c>
-      <c r="D14" s="118"/>
+      <c r="D14" s="116"/>
       <c r="E14" s="75">
         <v>792</v>
       </c>
@@ -67928,10 +67928,10 @@
       <c r="B16" s="70">
         <v>2.6249999999999999E-2</v>
       </c>
-      <c r="C16" s="118">
+      <c r="C16" s="116">
         <v>47817</v>
       </c>
-      <c r="D16" s="118"/>
+      <c r="D16" s="116"/>
       <c r="E16" s="75">
         <v>698</v>
       </c>
@@ -67958,10 +67958,10 @@
       <c r="B18" s="70">
         <v>3.3750000000000002E-2</v>
       </c>
-      <c r="C18" s="118">
+      <c r="C18" s="116">
         <v>48468</v>
       </c>
-      <c r="D18" s="118"/>
+      <c r="D18" s="116"/>
       <c r="E18" s="75">
         <v>859</v>
       </c>
@@ -67988,10 +67988,10 @@
       <c r="B20" s="70">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="C20" s="118">
+      <c r="C20" s="116">
         <v>49350</v>
       </c>
-      <c r="D20" s="118"/>
+      <c r="D20" s="116"/>
       <c r="E20" s="75">
         <v>989</v>
       </c>
@@ -68018,10 +68018,10 @@
       <c r="B22" s="70">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C22" s="118">
+      <c r="C22" s="116">
         <v>52322</v>
       </c>
-      <c r="D22" s="118"/>
+      <c r="D22" s="116"/>
       <c r="E22" s="75">
         <v>393</v>
       </c>
@@ -68048,10 +68048,10 @@
       <c r="B24" s="70">
         <v>4.6249999999999999E-2</v>
       </c>
-      <c r="C24" s="118">
+      <c r="C24" s="116">
         <v>53401</v>
       </c>
-      <c r="D24" s="118"/>
+      <c r="D24" s="116"/>
       <c r="E24" s="75">
         <v>984</v>
       </c>
@@ -68132,16 +68132,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
@@ -68156,6 +68146,16 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
